--- a/VerveStacks_MEX_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_MEX_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AF0BB3-0E6F-432C-A21A-7851CCE8118C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11BFA1D-A88A-4A34-BAB6-7C46D1C71D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5294,7 +5294,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74CABF8B-51FE-4BEA-88DD-2ACD3813619B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEA02E3-F583-4926-8B01-1DD5967A797A}">
   <dimension ref="B3:I232"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_MEX_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_MEX_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11BFA1D-A88A-4A34-BAB6-7C46D1C71D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A9349B-AAE6-4876-A7EA-8592104BBB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5294,7 +5294,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEA02E3-F583-4926-8B01-1DD5967A797A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D6B4B7-FF3B-4644-AB3C-E880C95AD021}">
   <dimension ref="B3:I232"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
